--- a/output/2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cappe industriali ad alta efficienza per aspirazione fumi/vapori/odori, filtri a labirinto, filtri antigrasso, filtri a carboni attivi, sistemi wet scrubbing; anche abbattitori di fuliggine. Verificata via mcaimpianti.eu, mcaimpianti-napoli.it, paginebianche.it.</t>
+          <t>Cappe industriali ad alta efficienza per aspirazione fumi/vapori/odori, filtri a labirinto, filtri antigrasso, filtri a carboni attivi, sistemi wet scrubbing; anche abbattitori di fuliggine. Verificata via mcaimpianti.eu, mcaimpianti-napoli.it, paginebianche.it. [DUPLICATO — vedi anche: 2026-09-03_00_Italia_Campania_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
